--- a/annotators/team/tg/annotated/bbc.242405.xlsx
+++ b/annotators/team/tg/annotated/bbc.242405.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\in-progress\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tabea\Desktop\Git\AURIS\annotators\team\tg\annotated\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB846EF-EEAC-44A1-A5C5-DEB19CB68001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59FA1BCE-7D57-485A-AA7F-E3D71932D8E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="16368" windowHeight="10836" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sentence-level annotation" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1375" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="431">
   <si>
     <t>ID</t>
   </si>
@@ -5958,9 +5958,7 @@
       <c r="F106" s="22" t="s">
         <v>385</v>
       </c>
-      <c r="G106" s="23" t="s">
-        <v>102</v>
-      </c>
+      <c r="G106" s="23"/>
       <c r="H106" s="24" t="str">
         <f t="shared" ca="1" si="11"/>
         <v/>
@@ -6167,7 +6165,7 @@
         <v>OLD</v>
       </c>
       <c r="G112" s="23" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="H112" s="24" t="str">
         <f t="shared" ca="1" si="11"/>
@@ -7323,9 +7321,7 @@
       <c r="F148" s="22" t="s">
         <v>385</v>
       </c>
-      <c r="G148" s="23" t="s">
-        <v>102</v>
-      </c>
+      <c r="G148" s="23"/>
       <c r="H148" s="24" t="str">
         <f t="shared" ca="1" si="15"/>
         <v/>
@@ -7671,7 +7667,7 @@
         <v>OLD</v>
       </c>
       <c r="G158" s="23" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="H158" s="24" t="str">
         <f t="shared" ca="1" si="15"/>
@@ -11308,7 +11304,7 @@
         <v/>
       </c>
       <c r="H270" s="24" t="str">
-        <f t="shared" ref="H269:H308" ca="1" si="27">IF(J270&lt;&gt;1,"",IF(I270="SBJ","CB","?"))</f>
+        <f t="shared" ref="H270:H308" ca="1" si="27">IF(J270&lt;&gt;1,"",IF(I270="SBJ","CB","?"))</f>
         <v/>
       </c>
       <c r="I270" s="25" t="str">
@@ -14830,7 +14826,7 @@
         <v/>
       </c>
       <c r="H375" s="24" t="str">
-        <f t="shared" ref="H374:H405" ca="1" si="35">IF(J375&lt;&gt;1,"",IF(I375="SBJ","CB","?"))</f>
+        <f t="shared" ref="H375:H405" ca="1" si="35">IF(J375&lt;&gt;1,"",IF(I375="SBJ","CB","?"))</f>
         <v/>
       </c>
       <c r="I375" s="25" t="str">
@@ -17019,9 +17015,7 @@
       <c r="F438" s="22" t="s">
         <v>385</v>
       </c>
-      <c r="G438" s="23" t="s">
-        <v>102</v>
-      </c>
+      <c r="G438" s="23"/>
       <c r="H438" s="24" t="str">
         <f t="shared" ca="1" si="37"/>
         <v/>
@@ -17387,7 +17381,7 @@
         <v>OLD</v>
       </c>
       <c r="G448" s="23" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="H448" s="24" t="str">
         <f t="shared" ca="1" si="37"/>
@@ -19587,7 +19581,7 @@
         <v/>
       </c>
       <c r="H515" s="24" t="str">
-        <f t="shared" ref="H514:H530" ca="1" si="43">IF(J515&lt;&gt;1,"",IF(I515="SBJ","CB","?"))</f>
+        <f t="shared" ref="H515:H530" ca="1" si="43">IF(J515&lt;&gt;1,"",IF(I515="SBJ","CB","?"))</f>
         <v/>
       </c>
       <c r="I515" s="25" t="str">
